--- a/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
+++ b/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
@@ -7,14 +7,20 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Battlecards" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Alertas (histórico)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Esquadrão de Combate" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Preços Atuais" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Radar ML" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Desempenho Próprio" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Limitações" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="⚠ Keywords é simulado" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Battlecards" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Alertas (histórico)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Esquadrão de Combate" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Preços Atuais" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Radar ML" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Desempenho Próprio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Google Shopping" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Keywords &amp; Leilão" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Concorrentes Descobertos" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Histórico Preço x Ads" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Catálogo" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Limitações" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,11 +62,16 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00B00020"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="001F2A44"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +98,11 @@
         <fgColor rgb="0027AE60"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -100,8 +116,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,7 +141,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -490,6 +510,1890 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Este relatório de keywords usa DADO SIMULADO — o Google Ads ainda não está conectado no Windsor.ai desta integração. Ver references/fontes-e-limitacoes.md.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>CAMPANHA</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>KEYWORD</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>CLICKS</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>CPC_MEDIO</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY_SCORE</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>IMPRESSION_SHARE</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>RANK_LOST</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>DOMINIOS_NO_LEILAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>joie suplementos</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>890</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>joie</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>3100</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>540</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>suplementos alimentares</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>whey protein</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>whey protein isolado</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1320</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (1x), vitafor.com.br (1x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>omega 3</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>980</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>polivitamínico</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>860</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>creatina monohidratada</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>640</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (1x), vitafor.com.br (1x)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>PRODUTO</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>CANDIDATO</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>ORIGEM</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>TITULO_VARIANTE</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>COMPONENTES_SEM_DADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>SKIN DOCTOR OFICIAL</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Sérum Facial Skin Doctor Vitamina C</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>presenca_ads, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>BLACK SKULL</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Sérum Facial Vitamina C Black Skull 30ml</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>VULT COSMETICOS</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Sérum Vitamina C Vult 30ml</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>presenca_ads, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>CENTRUM OFICIAL</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Multivitamínico Feminino Centrum</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>presenca_ads, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>GROWTH SUPPLEMENTS</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Polivitamínico Feminino Growth 60 cápsulas</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>BLACK SKULL</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Whey Protein Isolado Black Skull 900g</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>manual, descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Whey Protein Concentrado Max Titanium 900g</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>GROWTH SUPPLEMENTS</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Whey Protein Isolado Growth 900g</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Creatina Joie</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>BLACK SKULL</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Creatina Black Skull Creatine 300g</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>preco, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Creatina Joie</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>manual, descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Creatina Monohidratada Max Titanium 300g</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>preco, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Creatina Joie</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>GROWTH SUPPLEMENTS</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Creatina Monohidratada Growth 300g</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>preco, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>(global — leilão)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>manual, auction_insight</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>(global — leilão)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>auction_insight</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>(global — leilão)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>auction_insight</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>(global — leilão)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>vitafor.com.br</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>auction_insight</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>vitafor.com.br</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>PRODUTO</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>CONCORRENTE</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>PRECO</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>TEM_ADS</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>NOSSA_POSICAO</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>CONCORRENTE_POSICAO</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>DISPUTANDO_DIRETO</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>KPI_QUEDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="E9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E15" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E16" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E17" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>NOME</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>MONITORANDO?</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>DETALHE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sérum facial vitamina c</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>polivitamínico feminino</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>whey protein isolado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Creatina Joie</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>candidato</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>creatina monohidratada 300g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Concorrente</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>blackskull.com.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Concorrente</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>growthsupplements.com.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Concorrente</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>candidato</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>O que este relatório CAPTURA automaticamente</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Preço, preço original, desconto, posição na busca e reviews de cada concorrente cadastrado, comparados com a rodada anterior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr"/>
+      <c r="B3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>O que NÃO captura</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Investimento real (R$) em Google Ads ou Meta Ads</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Não existe fonte pública para o gasto de terceiros em nenhuma plataforma. Não é estimado, não é inventado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Anúncios pagos do Google na SERP</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>O scraper de SERP usado não retorna paidResults/paidProducts — confirmado vazio mesmo em termos com anúncio comprovado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Contagem de anúncios ativos (Meta Ad Library / Google Ads Transparency Center)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>É sinal de ATIVIDADE, não de valor gasto, e hoje é capturado manualmente via --ads-manual (o script não navega esses painéis sozinho).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Posição no Mercado Livre = patrocinado?</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>O scraper não confirma se um item específico é Mercado Ads ou orgânico — subida de posição é tratada como proxy, não prova.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Como cobrir melhor o pago</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Veja references/fontes-e-limitacoes.md e a skill brand-bidding-monitor para os métodos manuais completos (SERP, Ad Library, Ads Transparency Center, Auction Insights).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -498,16 +2402,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>War Room — Joie</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Gerado em 2026-08-01 05:59 UTC | cadência sugerida: 6h</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Gerado em 2026-08-01 09:56 UTC | cadência sugerida: 6h</t>
         </is>
       </c>
     </row>
@@ -516,12 +2420,12 @@
       <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>INDICADOR</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
@@ -564,7 +2468,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -604,7 +2508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -627,399 +2531,399 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>SEVERIDADE</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>NIVEL</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>CONCORRENTE</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>RESUMO</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>IMPACTO_CONCORRENCIA</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>IMPACTO_VOLUME</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>ESTRATEGIA_IMEDIATA</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>KPIS_IMPACTADOS</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>EVIDENCIA_URL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>queda_preco</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>agressiva</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Black Skull baixou o preço de 'Faciderm' de R$ 89.90 para R$ 71.90 (-20.0%).</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Sinal de liquidação de estoque, novo substituto ou guerra de preço deliberada. Risco alto de canibalização no curto prazo.</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Estimativa por elasticidade deve ser tratada como piso — quedas agressivas convertem desproporcionalmente mais (efeito ancoragem). Estimativa: +30.0% de deslocamento de demanda (a seu favor), usando elasticidade configurada (-1.5) x variação de preço observada (-20.0%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 104.90, ROAS 5.00, CTR 6.47% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Price-match seletivo só nos SKUs mais expostos, não na linha toda; Reforçar prova social (reviews/garantia) para justificar não seguir a queda; Campanha de retenção/e-mail para base já convertida; Checar se é liquidação temporária antes de comprometer margem de forma permanente</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Margem de contribuição, ROAS, CAC, Share of search/Buy Box, Taxa de conversão, Ticket médio</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>novo_desconto</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Black Skull passou a oferecer 20% de desconto em 'Faciderm' (antes 0%).</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Desconto por tempo limitado costuma converter mais rápido que uma baixa de preço permanente (efeito urgência).</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Tratar como a queda de preço equivalente, com efeito concentrado na janela do cupom (não distribuído).</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>Cupom-espelho de curta duração no produto equivalente; Destacar frete grátis/parcelamento se não puder cobrir o desconto; Se o cupom for sazonal (Black Friday etc.), sincronizar campanha própria à mesma data em vez de reagir isolado</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>CTR, Taxa de conversão, CAC no período do cupom, ROAS da campanha ativa</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>novo_entrante</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Growth Supplements</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Growth Supplements apareceu pela 1a vez na busca de 'Faciderm' (posição 2).</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Aumento da concorrência direta no mesmo termo de busca; dilui share entre mais players.</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Risco difuso, maior quanto mais barato/melhor avaliado for o novo entrante.</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Cadastrar o novo concorrente no config.json para monitorar nas próximas rodadas; Avaliar se ele compete por preço, marca ou diferencial de produto para calibrar a resposta</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>Share of search, Posição média, Taxa de conversão</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>https://mercadolivre.com.br/simulado/growth-faciderm</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>salto_visibilidade_ml</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Black Skull ganhou visibilidade em 'Amaze': subiu da posição 4 para 1 e reviews de 60 para 95.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Mais impressões para o concorrente no mesmo termo; nas primeiras posições do ML o CTR cai muito rápido por posição perdida.</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Correlacionado com perda de share of search; não quantificável com precisão sem dados de leilão — tratar como alerta de atenção.</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Revisar ficha do produto próprio (título, imagens, reviews, perguntas respondidas); Considerar aumentar lance de Mercado Ads no termo, se já houver campanha ativa; Checar se o concorrente lançou promoção/frete que também ajuda o ranqueamento</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Posição média na busca, CTR, Taxa de conversão, Impression share (Mercado Ads)</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>https://mercadolivre.com.br/simulado/black-skull-amaze</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>concorrente_sumiu</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Growth Supplements</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Growth Supplements sumiu da busca de 'Amaze' (estava na posição 1). Hipótese: ruptura de estoque ou pausa de campanha — não confirmado.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Janela de oportunidade temporária — menos competição direta pelo termo/posição.</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Oportunidade de ganho de share enquanto durar; não é permanente até confirmar (pode ser reposição de estoque em dias).</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Aumentar temporariamente investimento em mídia no termo/SKU equivalente para capturar a demanda órfã; Não reduzir preço proativamente — a demanda já não tem para onde ir</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>Share of search, Volume/conversão do SKU equivalente, ROAS</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>https://mercadolivre.com.br/simulado/growth-amaze</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>aumento_preco_concorrente</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>moderada</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Black Skull subiu o preço de 'Linha Joie Fit' de R$ 119.90 para R$ 129.90 (+8.3%).</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Janela real de oportunidade para ganhar posição/Buy Box e volume sem sacrificar margem.</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Ganho potencial relevante (ver estimativa por elasticidade, sentido positivo). Estimativa: -12.5% de deslocamento de demanda (a favor do concorrente), usando elasticidade configurada (-1.5) x variação de preço observada (+8.3%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 134.49, ROAS 3.55, CTR 2.29% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Reforçar investimento em mídia paga no SKU equivalente enquanto a vantagem dura; Atualizar comparativos de preço em conteúdo/anúncio</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>Share of search/impressões, ROAS, CAC</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>https://mercadolivre.com.br/simulado/black-skull-whey</t>
         </is>
@@ -1030,13 +2934,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1054,1054 +2958,434 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>SEVERIDADE</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>NIVEL</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>CONCORRENTE</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>RESUMO</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>IMPACTO_CONCORRENCIA</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>IMPACTO_VOLUME</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>ESTRATEGIA_IMEDIATA</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>KPIS_IMPACTADOS</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>EVIDENCIA_URL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 05:59 UTC</t>
+          <t>2026-08-01 09:56 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>queda_preco</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>agressiva</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Black Skull baixou o preço de 'Faciderm' de R$ 89.90 para R$ 71.90 (-20.0%).</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sinal de liquidação de estoque, novo substituto ou guerra de preço deliberada. Risco alto de canibalização no curto prazo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Estimativa por elasticidade deve ser tratada como piso — quedas agressivas convertem desproporcionalmente mais (efeito ancoragem). Estimativa: +30.0% de deslocamento de demanda (a seu favor), usando elasticidade configurada (-1.5) x variação de preço observada (-20.0%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 104.90, ROAS 5.00, CTR 6.47% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Price-match seletivo só nos SKUs mais expostos, não na linha toda; Reforçar prova social (reviews/garantia) para justificar não seguir a queda; Campanha de retenção/e-mail para base já convertida; Checar se é liquidação temporária antes de comprometer margem de forma permanente</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Margem de contribuição, ROAS, CAC, Share of search/Buy Box, Taxa de conversão, Ticket médio</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:56 UTC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>novo_desconto</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Black Skull passou a oferecer 20% de desconto em 'Faciderm' (antes 0%).</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Desconto por tempo limitado costuma converter mais rápido que uma baixa de preço permanente (efeito urgência).</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Tratar como a queda de preço equivalente, com efeito concentrado na janela do cupom (não distribuído).</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Cupom-espelho de curta duração no produto equivalente; Destacar frete grátis/parcelamento se não puder cobrir o desconto; Se o cupom for sazonal (Black Friday etc.), sincronizar campanha própria à mesma data em vez de reagir isolado</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CTR, Taxa de conversão, CAC no período do cupom, ROAS da campanha ativa</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:56 UTC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>novo_entrante</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Growth Supplements apareceu pela 1a vez na busca de 'Faciderm' (posição 2).</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aumento da concorrência direta no mesmo termo de busca; dilui share entre mais players.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Risco difuso, maior quanto mais barato/melhor avaliado for o novo entrante.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Cadastrar o novo concorrente no config.json para monitorar nas próximas rodadas; Avaliar se ele compete por preço, marca ou diferencial de produto para calibrar a resposta</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Share of search, Posição média, Taxa de conversão</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://mercadolivre.com.br/simulado/growth-faciderm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:56 UTC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>salto_visibilidade_ml</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Black Skull ganhou visibilidade em 'Amaze': subiu da posição 4 para 1 e reviews de 60 para 95.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mais impressões para o concorrente no mesmo termo; nas primeiras posições do ML o CTR cai muito rápido por posição perdida.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Correlacionado com perda de share of search; não quantificável com precisão sem dados de leilão — tratar como alerta de atenção.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Revisar ficha do produto próprio (título, imagens, reviews, perguntas respondidas); Considerar aumentar lance de Mercado Ads no termo, se já houver campanha ativa; Checar se o concorrente lançou promoção/frete que também ajuda o ranqueamento</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Posição média na busca, CTR, Taxa de conversão, Impression share (Mercado Ads)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://mercadolivre.com.br/simulado/black-skull-amaze</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:56 UTC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>concorrente_sumiu</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Growth Supplements sumiu da busca de 'Amaze' (estava na posição 1). Hipótese: ruptura de estoque ou pausa de campanha — não confirmado.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Janela de oportunidade temporária — menos competição direta pelo termo/posição.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Oportunidade de ganho de share enquanto durar; não é permanente até confirmar (pode ser reposição de estoque em dias).</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Aumentar temporariamente investimento em mídia no termo/SKU equivalente para capturar a demanda órfã; Não reduzir preço proativamente — a demanda já não tem para onde ir</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Share of search, Volume/conversão do SKU equivalente, ROAS</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://mercadolivre.com.br/simulado/growth-amaze</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:56 UTC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>aumento_preco_concorrente</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>agressiva</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>moderada</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Black Skull subiu o preço de 'Faciderm' de R$ 71.90 para R$ 89.90 (+25.0%).</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Vantagem de preço grande; janela de oportunidade forte.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Ganho potencial alto (ver estimativa por elasticidade, sentido positivo) — tratar como teto otimista. Estimativa: -37.6% de deslocamento de demanda (a favor do concorrente), usando elasticidade configurada (-1.5) x variação de preço observada (+25.0%). Premissa, não dado medido.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Reforçar investimento em mídia paga no SKU equivalente; Considerar reduzir desconto próprio parcialmente para capturar margem, permanecendo mais barato; Atualizar comparativos de preço em conteúdo/anúncio</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Share of search/impressões, ROAS, Margem de contribuição, CAC</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-01 05:59 UTC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>concorrente_sumiu</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Growth Supplements sumiu da busca de 'Faciderm' (estava na posição 2). Hipótese: ruptura de estoque ou pausa de campanha — não confirmado.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Janela de oportunidade temporária — menos competição direta pelo termo/posição.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Oportunidade de ganho de share enquanto durar; não é permanente até confirmar (pode ser reposição de estoque em dias).</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Aumentar temporariamente investimento em mídia no termo/SKU equivalente para capturar a demanda órfã; Não reduzir preço proativamente — a demanda já não tem para onde ir</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Share of search, Volume/conversão do SKU equivalente, ROAS</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/growth-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-01 05:59 UTC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>novo_entrante</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Growth Supplements apareceu pela 1a vez na busca de 'Amaze' (posição 1).</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Aumento da concorrência direta no mesmo termo de busca; dilui share entre mais players.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Risco difuso, maior quanto mais barato/melhor avaliado for o novo entrante.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Cadastrar o novo concorrente no config.json para monitorar nas próximas rodadas; Avaliar se ele compete por preço, marca ou diferencial de produto para calibrar a resposta</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Share of search, Posição média, Taxa de conversão</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/growth-amaze</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-01 05:59 UTC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>queda_preco</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>moderada</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Black Skull baixou o preço de 'Linha Joie Fit' de R$ 129.90 para R$ 119.90 (-7.7%).</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Diferencial de preço passa a aparecer em comparações; risco real de perder Buy Box/1a posição em produto-commodity.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Perceptível na conversão do SKU equivalente em 3-7 dias (ver estimativa por elasticidade). Estimativa: +11.5% de deslocamento de demanda (a seu favor), usando elasticidade configurada (-1.5) x variação de preço observada (-7.7%). Premissa, não dado medido.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Avaliar price-match parcial (cobrir só a diferença que tira do 'melhor preço'); Reforçar frete grátis/parcelamento como diferencial não-preço; Ativar cupom pontual no SKU equivalente</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>CAC, ROAS do SKU, Taxa de conversão, Posição média/Buy Box no ML, Ticket médio</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-whey</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-01 05:59 UTC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>queda_preco</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>agressiva</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Black Skull baixou o preço de 'Faciderm' de R$ 89.90 para R$ 71.90 (-20.0%).</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Sinal de liquidação de estoque, novo substituto ou guerra de preço deliberada. Risco alto de canibalização no curto prazo.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Estimativa por elasticidade deve ser tratada como piso — quedas agressivas convertem desproporcionalmente mais (efeito ancoragem). Estimativa: +30.0% de deslocamento de demanda (a seu favor), usando elasticidade configurada (-1.5) x variação de preço observada (-20.0%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 104.90, ROAS 5.00, CTR 6.47% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Price-match seletivo só nos SKUs mais expostos, não na linha toda; Reforçar prova social (reviews/garantia) para justificar não seguir a queda; Campanha de retenção/e-mail para base já convertida; Checar se é liquidação temporária antes de comprometer margem de forma permanente</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Margem de contribuição, ROAS, CAC, Share of search/Buy Box, Taxa de conversão, Ticket médio</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-08-01 05:59 UTC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>novo_desconto</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Black Skull passou a oferecer 20% de desconto em 'Faciderm' (antes 0%).</t>
+          <t>Black Skull subiu o preço de 'Linha Joie Fit' de R$ 119.90 para R$ 129.90 (+8.3%).</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Desconto por tempo limitado costuma converter mais rápido que uma baixa de preço permanente (efeito urgência).</t>
+          <t>Janela real de oportunidade para ganhar posição/Buy Box e volume sem sacrificar margem.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tratar como a queda de preço equivalente, com efeito concentrado na janela do cupom (não distribuído).</t>
+          <t>Ganho potencial relevante (ver estimativa por elasticidade, sentido positivo). Estimativa: -12.5% de deslocamento de demanda (a favor do concorrente), usando elasticidade configurada (-1.5) x variação de preço observada (+8.3%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 134.49, ROAS 3.55, CTR 2.29% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cupom-espelho de curta duração no produto equivalente; Destacar frete grátis/parcelamento se não puder cobrir o desconto; Se o cupom for sazonal (Black Friday etc.), sincronizar campanha própria à mesma data em vez de reagir isolado</t>
+          <t>Reforçar investimento em mídia paga no SKU equivalente enquanto a vantagem dura; Atualizar comparativos de preço em conteúdo/anúncio</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>CTR, Taxa de conversão, CAC no período do cupom, ROAS da campanha ativa</t>
+          <t>Share of search/impressões, ROAS, CAC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-08-01 05:59 UTC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>novo_entrante</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Growth Supplements apareceu pela 1a vez na busca de 'Faciderm' (posição 2).</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Aumento da concorrência direta no mesmo termo de busca; dilui share entre mais players.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Risco difuso, maior quanto mais barato/melhor avaliado for o novo entrante.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Cadastrar o novo concorrente no config.json para monitorar nas próximas rodadas; Avaliar se ele compete por preço, marca ou diferencial de produto para calibrar a resposta</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Share of search, Posição média, Taxa de conversão</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/growth-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-08-01 05:59 UTC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>salto_visibilidade_ml</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Black Skull ganhou visibilidade em 'Amaze': subiu da posição 4 para 1 e reviews de 60 para 95.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Mais impressões para o concorrente no mesmo termo; nas primeiras posições do ML o CTR cai muito rápido por posição perdida.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Correlacionado com perda de share of search; não quantificável com precisão sem dados de leilão — tratar como alerta de atenção.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Revisar ficha do produto próprio (título, imagens, reviews, perguntas respondidas); Considerar aumentar lance de Mercado Ads no termo, se já houver campanha ativa; Checar se o concorrente lançou promoção/frete que também ajuda o ranqueamento</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Posição média na busca, CTR, Taxa de conversão, Impression share (Mercado Ads)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-amaze</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-08-01 05:59 UTC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>concorrente_sumiu</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Growth Supplements sumiu da busca de 'Amaze' (estava na posição 1). Hipótese: ruptura de estoque ou pausa de campanha — não confirmado.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Janela de oportunidade temporária — menos competição direta pelo termo/posição.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Oportunidade de ganho de share enquanto durar; não é permanente até confirmar (pode ser reposição de estoque em dias).</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Aumentar temporariamente investimento em mídia no termo/SKU equivalente para capturar a demanda órfã; Não reduzir preço proativamente — a demanda já não tem para onde ir</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Share of search, Volume/conversão do SKU equivalente, ROAS</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/growth-amaze</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-08-01 05:59 UTC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>aumento_preco_concorrente</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>moderada</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Black Skull subiu o preço de 'Linha Joie Fit' de R$ 119.90 para R$ 129.90 (+8.3%).</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Janela real de oportunidade para ganhar posição/Buy Box e volume sem sacrificar margem.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Ganho potencial relevante (ver estimativa por elasticidade, sentido positivo). Estimativa: -12.5% de deslocamento de demanda (a favor do concorrente), usando elasticidade configurada (-1.5) x variação de preço observada (+8.3%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 134.49, ROAS 3.55, CTR 2.29% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Reforçar investimento em mídia paga no SKU equivalente enquanto a vantagem dura; Atualizar comparativos de preço em conteúdo/anúncio</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Share of search/impressões, ROAS, CAC</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-whey</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-08-01 03:11 UTC</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>queda_preco</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>agressiva</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Black Skull baixou o preço de 'Faciderm' de R$ 89.90 para R$ 71.90 (-20.0%).</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sinal de liquidação de estoque, novo substituto ou guerra de preço deliberada. Risco alto de canibalização no curto prazo.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Estimativa por elasticidade deve ser tratada como piso — quedas agressivas convertem desproporcionalmente mais (efeito ancoragem). Estimativa: +30.0% de deslocamento de demanda (a seu favor), usando elasticidade configurada (-1.5) x variação de preço observada (-20.0%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 104.90, ROAS 5.00, CTR 6.47% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Price-match seletivo só nos SKUs mais expostos, não na linha toda; Reforçar prova social (reviews/garantia) para justificar não seguir a queda; Campanha de retenção/e-mail para base já convertida; Checar se é liquidação temporária antes de comprometer margem de forma permanente</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Margem de contribuição, ROAS, CAC, Share of search/Buy Box, Taxa de conversão, Ticket médio</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-08-01 03:11 UTC</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>novo_desconto</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Black Skull passou a oferecer 20% de desconto em 'Faciderm' (antes 0%).</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Desconto por tempo limitado costuma converter mais rápido que uma baixa de preço permanente (efeito urgência).</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Tratar como a queda de preço equivalente, com efeito concentrado na janela do cupom (não distribuído).</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Cupom-espelho de curta duração no produto equivalente; Destacar frete grátis/parcelamento se não puder cobrir o desconto; Se o cupom for sazonal (Black Friday etc.), sincronizar campanha própria à mesma data em vez de reagir isolado</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>CTR, Taxa de conversão, CAC no período do cupom, ROAS da campanha ativa</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-08-01 03:11 UTC</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>novo_entrante</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Growth Supplements apareceu pela 1a vez na busca de 'Faciderm' (posição 2).</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Aumento da concorrência direta no mesmo termo de busca; dilui share entre mais players.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Risco difuso, maior quanto mais barato/melhor avaliado for o novo entrante.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Cadastrar o novo concorrente no config.json para monitorar nas próximas rodadas; Avaliar se ele compete por preço, marca ou diferencial de produto para calibrar a resposta</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Share of search, Posição média, Taxa de conversão</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/growth-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-08-01 03:11 UTC</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>salto_visibilidade_ml</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Black Skull ganhou visibilidade em 'Amaze': subiu da posição 4 para 1 e reviews de 60 para 95.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Mais impressões para o concorrente no mesmo termo; nas primeiras posições do ML o CTR cai muito rápido por posição perdida.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Correlacionado com perda de share of search; não quantificável com precisão sem dados de leilão — tratar como alerta de atenção.</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Revisar ficha do produto próprio (título, imagens, reviews, perguntas respondidas); Considerar aumentar lance de Mercado Ads no termo, se já houver campanha ativa; Checar se o concorrente lançou promoção/frete que também ajuda o ranqueamento</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Posição média na busca, CTR, Taxa de conversão, Impression share (Mercado Ads)</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-amaze</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-08-01 03:11 UTC</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>concorrente_sumiu</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Growth Supplements sumiu da busca de 'Amaze' (estava na posição 1). Hipótese: ruptura de estoque ou pausa de campanha — não confirmado.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Janela de oportunidade temporária — menos competição direta pelo termo/posição.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Oportunidade de ganho de share enquanto durar; não é permanente até confirmar (pode ser reposição de estoque em dias).</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Aumentar temporariamente investimento em mídia no termo/SKU equivalente para capturar a demanda órfã; Não reduzir preço proativamente — a demanda já não tem para onde ir</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Share of search, Volume/conversão do SKU equivalente, ROAS</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/growth-amaze</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-08-01 03:11 UTC</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>aumento_preco_concorrente</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>moderada</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Black Skull subiu o preço de 'Linha Joie Fit' de R$ 119.90 para R$ 129.90 (+8.3%).</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Janela real de oportunidade para ganhar posição/Buy Box e volume sem sacrificar margem.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Ganho potencial relevante (ver estimativa por elasticidade, sentido positivo). Estimativa: -12.5% de deslocamento de demanda (a favor do concorrente), usando elasticidade configurada (-1.5) x variação de preço observada (+8.3%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 134.49, ROAS 3.55, CTR 2.29% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Reforçar investimento em mídia paga no SKU equivalente enquanto a vantagem dura; Atualizar comparativos de preço em conteúdo/anúncio</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Share of search/impressões, ROAS, CAC</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
         <is>
           <t>https://mercadolivre.com.br/simulado/black-skull-whey</t>
         </is>
@@ -2112,7 +3396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2130,224 +3414,224 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>AGENTE</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>TIPO_ALERTA</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>CONCORRENTE</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>RESUMO</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Agente de Precificação e Margem</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>AGUARDANDO AUTORIZAÇÃO</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>queda_preco</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Black Skull baixou o preço de 'Faciderm' de R$ 89.90 para R$ 71.90 (-20.0%).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Agente de Precificação e Margem</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>MONITORANDO</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>novo_desconto</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Black Skull passou a oferecer 20% de desconto em 'Faciderm' (antes 0%).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Agente de Marketplace (Mercado Livre Ops)</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>MONITORANDO</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>novo_entrante</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Growth Supplements</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Growth Supplements apareceu pela 1a vez na busca de 'Faciderm' (posição 2).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Agente de Marketplace (Mercado Livre Ops)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>MONITORANDO</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>salto_visibilidade_ml</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Black Skull ganhou visibilidade em 'Amaze': subiu da posição 4 para 1 e reviews de 60 para 95.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Agente de Marketplace (Mercado Livre Ops)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>MONITORANDO</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>concorrente_sumiu</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Growth Supplements</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Growth Supplements sumiu da busca de 'Amaze' (estava na posição 1). Hipótese: ruptura de estoque ou pausa de campanha — não confirmado.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Agente de Precificação e Margem</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>MONITORANDO</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>aumento_preco_concorrente</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Black Skull subiu o preço de 'Linha Joie Fit' de R$ 119.90 para R$ 129.90 (+8.3%).</t>
         </is>
@@ -2358,7 +3642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2381,57 +3665,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>CONCORRENTE</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>SELLER</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>ORIGINAL_PRICE</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>DISCOUNT_PCT</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>POSITION</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>TOTAL_LISTAGENS</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>REVIEWS</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -2614,7 +3898,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2635,47 +3919,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>QUEM</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>POSITION</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>DISCOUNT_PCT</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>REVIEWS</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>FRETE_GRATIS</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>PATROCINADO</t>
         </is>
@@ -2709,35 +3993,35 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>NÓS</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="C3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="10" t="n">
+      <c r="D3" s="11" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="F3" s="11" t="n">
         <v>340</v>
       </c>
-      <c r="G3" s="10" t="n">
+      <c r="G3" s="11" t="n">
         <v>4.8</v>
       </c>
-      <c r="H3" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="H3" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>desconhecido</t>
         </is>
@@ -2746,149 +4030,149 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>910</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>480</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>desconhecido</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" t="n">
         <v>20</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F6" t="n">
         <v>365</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" t="n">
         <v>4.6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>210</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H6" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>desconhecido</t>
-        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Black Skull</t>
+          <t>Growth Supplements</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>129.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>910</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>NÓS</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E8" s="10" t="n">
+      <c r="C8" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="10" t="n">
-        <v>480</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H8" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H8" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>desconhecido</t>
         </is>
@@ -2899,7 +4183,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2925,72 +4209,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>SPEND</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>IMPRESSIONS</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>CLICKS</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>CTR_PCT</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>CPC</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>CONVERSIONS</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>CONVERSIONS_VALUE</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>CPA</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>GA4_SESSIONS</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>GA4_ENGAJAMENTO_PCT</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>GA4_CONVERSAO_PCT</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>CAMPANHAS</t>
         </is>
@@ -3145,112 +4429,315 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>O que este relatório CAPTURA automaticamente</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr"/>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>PRODUTO</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>QUEM</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>POSITION</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>PRICE</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>DISCOUNT_PCT</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>REVIEWS</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>RATING</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>FRETE_GRATIS</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>PATROCINADO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Mercado Livre</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Preço, preço original, desconto, posição na busca e reviews de cada concorrente cadastrado, comparados com a rodada anterior.</t>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H2" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr"/>
-      <c r="B3" s="5" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>88</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>O que NÃO captura</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>640</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Investimento real (R$) em Google Ads ou Meta Ads</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Não existe fonte pública para o gasto de terceiros em nenhuma plataforma. Não é estimado, não é inventado.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>310</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nao</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Anúncios pagos do Google na SERP</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>O scraper de SERP usado não retorna paidResults/paidProducts — confirmado vazio mesmo em termos com anúncio comprovado.</t>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H6" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>nao</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Contagem de anúncios ativos (Meta Ad Library / Google Ads Transparency Center)</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>É sinal de ATIVIDADE, não de valor gasto, e hoje é capturado manualmente via --ads-manual (o script não navega esses painéis sozinho).</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" t="n">
+        <v>210</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Posição no Mercado Livre = patrocinado?</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>O scraper não confirma se um item específico é Mercado Ads ou orgânico — subida de posição é tratada como proxy, não prova.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Como cobrir melhor o pago</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Veja references/fontes-e-limitacoes.md e a skill brand-bidding-monitor para os métodos manuais completos (SERP, Ad Library, Ads Transparency Center, Auction Insights).</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H8" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>

--- a/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
+++ b/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
@@ -2411,7 +2411,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gerado em 2026-08-01 09:56 UTC | cadência sugerida: 6h</t>
+          <t>Gerado em 2026-08-01 10:11 UTC | cadência sugerida: 6h</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:56 UTC</t>
+          <t>2026-08-01 10:11 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-01 09:56 UTC</t>
+          <t>2026-08-01 10:11 UTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:56 UTC</t>
+          <t>2026-08-01 10:11 UTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-01 09:56 UTC</t>
+          <t>2026-08-01 10:11 UTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-01 09:56 UTC</t>
+          <t>2026-08-01 10:11 UTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-01 09:56 UTC</t>
+          <t>2026-08-01 10:11 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3968,185 +3968,185 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>365</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H4" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>desconhecido</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F5" t="n">
         <v>95</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G5" t="n">
         <v>4.3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>NÓS</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D6" s="11" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F6" s="11" t="n">
         <v>340</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G6" s="11" t="n">
         <v>4.8</v>
       </c>
-      <c r="H3" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="H6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>desconhecido</t>
         </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>910</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>480</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H5" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>desconhecido</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" t="n">
-        <v>365</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Faciderm</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Growth Supplements</t>
+          <t>Black Skull</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>68.90000000000001</v>
+        <v>129.9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>910</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Faciderm</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -4155,22 +4155,22 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>149.9</v>
+        <v>129.9</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>210</v>
+        <v>480</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H8" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -4497,105 +4497,105 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2" t="n">
+        <v>210</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H3" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>NÓS</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="11" t="n">
+      <c r="C4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E4" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="F4" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="G2" s="11" t="n">
+      <c r="G4" s="11" t="n">
         <v>4.8</v>
       </c>
-      <c r="H2" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>88</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>124.9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>640</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H4" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
@@ -4604,112 +4604,112 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Amaze</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Max Titanium</t>
+          <t>Growth Supplements</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>89.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>310</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H6" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>nao</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>640</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Faciderm</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Black Skull</t>
+          <t>Max Titanium</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>74.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>210</v>
+        <v>310</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Faciderm</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -4718,26 +4718,26 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>149.9</v>
+        <v>129.9</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H8" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
     </row>

--- a/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
+++ b/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
@@ -2411,7 +2411,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gerado em 2026-08-01 10:11 UTC | cadência sugerida: 6h</t>
+          <t>Gerado em 2026-08-01 10:24 UTC | cadência sugerida: 6h</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 10:11 UTC</t>
+          <t>2026-08-01 10:24 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-01 10:11 UTC</t>
+          <t>2026-08-01 10:24 UTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01 10:11 UTC</t>
+          <t>2026-08-01 10:24 UTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-01 10:11 UTC</t>
+          <t>2026-08-01 10:24 UTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-01 10:11 UTC</t>
+          <t>2026-08-01 10:24 UTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-01 10:11 UTC</t>
+          <t>2026-08-01 10:24 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3968,123 +3968,123 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>910</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>480</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H3" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>desconhecido</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E4" t="n">
         <v>20</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F4" t="n">
         <v>365</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G4" t="n">
         <v>4.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H4" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>desconhecido</t>
-        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amaze</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Black Skull</t>
+          <t>Growth Supplements</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>84.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Amaze</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -4093,19 +4093,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>99.90000000000001</v>
+        <v>149.9</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>340</v>
+        <v>210</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H6" s="11" t="b">
         <v>1</v>
@@ -4119,7 +4119,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Amaze</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4131,22 +4131,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>129.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>910</v>
+        <v>95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Amaze</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -4155,22 +4155,22 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>129.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>480</v>
+        <v>340</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H8" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Faciderm</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4511,16 +4511,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>74.90000000000001</v>
+        <v>124.9</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>210</v>
+        <v>640</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -4532,44 +4532,44 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E3" s="11" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="11" t="n">
-        <v>95</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H3" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>sim</t>
+      <c r="F3" t="n">
+        <v>310</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nao</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Amaze</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -4578,166 +4578,166 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>99.90000000000001</v>
+        <v>129.9</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H4" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" t="n">
+        <v>210</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H7" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Growth Supplements</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D8" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F8" t="n">
         <v>88</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G8" t="n">
         <v>4.6</v>
       </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>124.9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>640</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Max Titanium</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>310</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>nao</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H8" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>nao</t>
         </is>
       </c>
     </row>

--- a/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
+++ b/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
@@ -2411,7 +2411,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gerado em 2026-08-01 10:24 UTC | cadência sugerida: 6h</t>
+          <t>Gerado em 2026-08-01 10:34 UTC | cadência sugerida: 6h</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 10:24 UTC</t>
+          <t>2026-08-01 10:34 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-01 10:24 UTC</t>
+          <t>2026-08-01 10:34 UTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01 10:24 UTC</t>
+          <t>2026-08-01 10:34 UTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-01 10:24 UTC</t>
+          <t>2026-08-01 10:34 UTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-01 10:24 UTC</t>
+          <t>2026-08-01 10:34 UTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-01 10:24 UTC</t>
+          <t>2026-08-01 10:34 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3968,7 +3968,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3980,111 +3980,111 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>129.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>365</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>910</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>NÓS</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E3" s="11" t="n">
+      <c r="C4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E4" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="11" t="n">
-        <v>480</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H3" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="F4" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H4" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>desconhecido</t>
         </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="E4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4" t="n">
-        <v>365</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Faciderm</t>
+          <t>Amaze</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Growth Supplements</t>
+          <t>Black Skull</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>68.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Faciderm</t>
+          <t>Amaze</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -4093,19 +4093,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>149.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="11" t="b">
         <v>1</v>
@@ -4119,7 +4119,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Amaze</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4131,22 +4131,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>84.90000000000001</v>
+        <v>129.9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>95</v>
+        <v>910</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Amaze</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -4155,22 +4155,22 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>99.90000000000001</v>
+        <v>129.9</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>340</v>
+        <v>480</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H8" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4511,65 +4511,65 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>124.9</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2" t="n">
+        <v>210</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
-        <v>640</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="D3" s="11" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="G3" s="11" t="n">
         <v>4.7</v>
       </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H3" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Max Titanium</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>310</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>nao</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Amaze</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -4578,166 +4578,166 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>129.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H4" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Faciderm</t>
+          <t>Amaze</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>88</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>640</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>310</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="n">
         <v>210</v>
       </c>
-      <c r="G5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E6" s="11" t="n">
+      <c r="G8" s="11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H8" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>95</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H6" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H7" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>88</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>sim</t>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>nao</t>
         </is>
       </c>
     </row>

--- a/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
+++ b/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
@@ -19,8 +19,12 @@
     <sheet name="Keywords &amp; Leilão" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Concorrentes Descobertos" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Histórico Preço x Ads" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Catálogo" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Limitações" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="GA4 Funil" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="GA4 Canais" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="GA4 Landing Pages" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="GA4 Diagnóstico" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Catálogo" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Limitações" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -71,7 +75,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +107,11 @@
         <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -116,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -142,6 +151,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2084,6 +2094,1696 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ETAPA</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>VALOR</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>% DO TOPO</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>% DA ANTERIOR</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>PERDIDOS</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>MAIOR VAZAMENTO</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>EVENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sessões</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>20310</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>tráfego que entrou no site</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Viu produto</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10770</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9540</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>visualizações de item (view_item)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Add ao carrinho</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2974</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7796</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>add_to_cart</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>528</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>2446</v>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>begin_checkout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Compra</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>199</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="E6" t="n">
+        <v>329</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>CANAL</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>DECISAO</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>SESSIONS</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>ENGAGEMENT_RATE</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>TX_CARRINHO</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>TX_CHECKOUT_P_CARRINHO</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>TX_COMPRA_P_CHECKOUT</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>TX_CONVERSAO</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>COMPRAS</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>RECEITA</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>RECEITA_POR_SESSAO</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>TICKET_MEDIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cross-network</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>escalar</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8819</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.09921759836716181</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2022857142857143</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4463276836158192</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.008957931738292324</v>
+      </c>
+      <c r="I2" t="n">
+        <v>79</v>
+      </c>
+      <c r="J2" t="n">
+        <v>38793.47</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.398851343689761</v>
+      </c>
+      <c r="L2" t="n">
+        <v>491.056582278481</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>escalar</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2891</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1743341404358353</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.01487374610861294</v>
+      </c>
+      <c r="I3" t="n">
+        <v>43</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30442.23</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="L3" t="n">
+        <v>707.9588372093023</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Organic Search</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>escalar</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1683</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6257</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1402257872846108</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2033898305084746</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0130718954248366</v>
+      </c>
+      <c r="I4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11206.89</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.658877005347593</v>
+      </c>
+      <c r="L4" t="n">
+        <v>509.4040909090909</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Referral</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>testar aumento</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>415</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5831</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5301204819277109</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2545454545454545</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3035714285714285</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.04096385542168675</v>
+      </c>
+      <c r="I5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10761.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>25.93192771084338</v>
+      </c>
+      <c r="L5" t="n">
+        <v>633.0441176470588</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Paid Search</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>escalar</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1571</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6092</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1858688733290897</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.136986301369863</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.01527689369828135</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9936.700000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.325079567154679</v>
+      </c>
+      <c r="L6" t="n">
+        <v>414.0291666666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>escalar</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>676</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2322</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2011834319526627</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2058823529411765</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3214285714285715</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.01331360946745562</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8514.790000000001</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12.59584319526627</v>
+      </c>
+      <c r="L7" t="n">
+        <v>946.0877777777779</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>testar aumento</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>79</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5443</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9620253164556962</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03947368421052631</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.02531645569620253</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1013.62</v>
+      </c>
+      <c r="K8" t="n">
+        <v>12.8306329113924</v>
+      </c>
+      <c r="L8" t="n">
+        <v>506.81</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Organic Social</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>revisar ou cortar</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>616</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1038961038961039</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.003246753246753247</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>393.12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.6381818181818182</v>
+      </c>
+      <c r="L9" t="n">
+        <v>196.56</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>corrigir</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2683</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1841</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0447260529258293</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0003727171077152441</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>121.52</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.04529258292955646</v>
+      </c>
+      <c r="L10" t="n">
+        <v>121.52</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Paid Shopping</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>corrigir</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>943</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4761399787910923</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0267260579064588</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>revisar ou cortar</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>revisar ou cortar</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>123</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.01626016260162602</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Organic Shopping</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>revisar ou cortar</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Paid Video</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>revisar ou cortar</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>PAGINA</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>SESSIONS</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>ENGAGEMENT_RATE</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>BOUNCE_RATE</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>TX_CARRINHO</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>COMPRAS</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>TX_CONVERSAO</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>RECEITA</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>SEM_COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8543</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1311014865972141</v>
+      </c>
+      <c r="F2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.007959733114830855</v>
+      </c>
+      <c r="H2" t="n">
+        <v>28392.58</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>/vitaminas-b5-b6-com-magnesio---1g-frasco-x-60-caps-softgel/p</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1726</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6101</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1483198146002317</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.009269988412514484</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4601.88</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>/produtos/faciderm/c</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1234</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07455429497568881</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005672609400324149</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1927.24</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>/busca</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1062</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7373</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.03389830508474576</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.004708097928436911</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1206.91</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>/produtos/magnesio/c</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1014</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6213</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1725838264299803</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01479289940828402</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5358.95</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>/tpower-testofen-fenogrego-30-caps-softgel/p</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>523</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8566</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01912045889101338</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001912045889101338</v>
+      </c>
+      <c r="H7" t="n">
+        <v>379.9</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>/garrafa-copa-joie/p</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>493</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0.6531</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>1.44421906693712</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>/joiefit/c</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>406</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5493</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.08866995073891626</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.007389162561576354</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1170.02</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>/amaze---1g-frasco-x-120-caps-softgel/p</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>389</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4833</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5167</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.07712082262210797</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005141388174807198</v>
+      </c>
+      <c r="H10" t="n">
+        <v>303.8</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>/produtos/c</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>331</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6133</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.148036253776435</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.006042296072507553</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1329.3</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>/colageno-verisol-em-po---sabor-frutas-vermelhas-450g/p</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>293</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>0.7611</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>0.07508532423208192</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>(sem página)</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>288</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>(not set)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>274</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>0.0145985401459854</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>/kit-magnesio-quelato-mais-calcio-600---60-caps-soft-gel---joie-suplementos-1/p</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>175</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6343</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.09142857142857143</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="H15" t="n">
+        <v>584.8</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>/faciderm---colageno-hidrolisado-e-vitamina-c-120-capsulas---135g---vitamina-para-a-pele-do-rosto/p</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>124</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>0.7016</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>/kit-magnesio-quelato-mais-colageno-verisol---joie-suplementos/p</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>0.6696</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>0.01739130434782609</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>/fale-conosco</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>0.6339</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>/curcuma-e-vitamina-c-joie---60-capsulas-600mg---auxilia-a-aumentar-a-imunidade/p</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>111</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>0.7117</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>/colageno-verisol-em-po---sabor-limao-450g/p</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>0.7692</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>0.0576923076923077</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>/oleo-de-cartamo---1g-frasco-x-120-caps-softgel/p</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2145.95</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>NÍVEL</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>ACHADO</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>DETALHE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Maior vazamento do funil: Checkout</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Só 17.8% da etapa anterior chega em 'Checkout' (528 de 2,974). É onde a correção tem o maior efeito absoluto no número de compras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Canal 'Paid Shopping' traz volume e não converte</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>943 sessões e 0 compra(s) no período, com 449 adições ao carrinho. Checar rastreamento de conversão desse canal antes de concluir que é audiência ruim — volume alto com zero compra costuma ser tag/atribuição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Engajamento de 'Direct' muito abaixo da mediana</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>27.1% de sessões engajadas contra mediana de 46.6% entre os canais, sobre 2,891 sessões. Sinal clássico de descasamento entre criativo/segmentação e a página de destino.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Engajamento de 'Unassigned' muito abaixo da mediana</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>23.2% de sessões engajadas contra mediana de 46.6% entre os canais, sobre 676 sessões. Sinal clássico de descasamento entre criativo/segmentação e a página de destino.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Engajamento de 'Paid Social' muito abaixo da mediana</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>18.4% de sessões engajadas contra mediana de 46.6% entre os canais, sobre 2,683 sessões. Sinal clássico de descasamento entre criativo/segmentação e a página de destino.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>9 landing page(s) com tráfego e nenhuma compra</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Maiores: /garrafa-copa-joie/p (493 sessões, 712 no carrinho); /colageno-verisol-em-po---sabor-frutas-vermelhas-450g/p (293 sessões, 22 no carrinho); (sem página) (288 sessões, 40 no carrinho). Priorize por sessão perdida, não por número de páginas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Concentração por dispositivo</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>mobile concentra 74% da receita. Pior conversão entre devices com volume: mobile (0.87%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Dependência de cliente novo</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>82% dos compradores do período compraram pela primeira vez (155 de 188). Quanto mais alto, mais o faturamento depende de aquisição paga e menos de base.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2274,7 +3974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2288,7 +3988,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>O que este relatório CAPTURA automaticamente</t>
         </is>
@@ -2312,7 +4012,7 @@
       <c r="B3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>O que NÃO captura</t>
         </is>
@@ -2411,7 +4111,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gerado em 2026-08-01 10:34 UTC | cadência sugerida: 6h</t>
+          <t>Gerado em 2026-08-01 10:55 UTC | cadência sugerida: 6h</t>
         </is>
       </c>
     </row>
@@ -3027,7 +4727,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 10:34 UTC</t>
+          <t>2026-08-01 10:55 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3089,7 +4789,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-01 10:34 UTC</t>
+          <t>2026-08-01 10:55 UTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3151,7 +4851,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01 10:34 UTC</t>
+          <t>2026-08-01 10:55 UTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3213,7 +4913,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-01 10:34 UTC</t>
+          <t>2026-08-01 10:55 UTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3275,7 +4975,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-01 10:34 UTC</t>
+          <t>2026-08-01 10:55 UTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3337,7 +5037,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-01 10:34 UTC</t>
+          <t>2026-08-01 10:55 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3968,7 +5668,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Faciderm</t>
+          <t>Amaze</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3980,173 +5680,173 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>95</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>340</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H3" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>desconhecido</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>910</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>480</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>desconhecido</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E6" t="n">
         <v>20</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F6" t="n">
         <v>365</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G6" t="n">
         <v>4.6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H4" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>desconhecido</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>95</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>340</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H6" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>desconhecido</t>
-        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Black Skull</t>
+          <t>Growth Supplements</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>129.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>910</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -4155,22 +5855,22 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>129.9</v>
+        <v>149.9</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>480</v>
+        <v>210</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H8" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -4497,105 +6197,105 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H2" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>88</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F2" t="n">
-        <v>210</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H2" t="b">
+      <c r="D4" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>640</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H4" t="b">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>95</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H3" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H4" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
@@ -4604,112 +6304,112 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amaze</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Growth Supplements</t>
+          <t>Max Titanium</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>76.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="G5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="G6" s="11" t="n">
         <v>4.6</v>
       </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>124.9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>640</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>sim</t>
+      <c r="H6" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>nao</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Max Titanium</t>
+          <t>Black Skull</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>89.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
-        <v>310</v>
+        <v>210</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -4718,26 +6418,26 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>129.9</v>
+        <v>149.9</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>210</v>
+        <v>95</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H8" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
     </row>

--- a/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
+++ b/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
@@ -4111,7 +4111,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gerado em 2026-08-01 10:55 UTC | cadência sugerida: 6h</t>
+          <t>Gerado em 2026-08-02 02:50 UTC | cadência sugerida: 6h</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 10:55 UTC</t>
+          <t>2026-08-02 02:50 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-01 10:55 UTC</t>
+          <t>2026-08-02 02:50 UTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01 10:55 UTC</t>
+          <t>2026-08-02 02:50 UTC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-01 10:55 UTC</t>
+          <t>2026-08-02 02:50 UTC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-01 10:55 UTC</t>
+          <t>2026-08-02 02:50 UTC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-01 10:55 UTC</t>
+          <t>2026-08-02 02:50 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">

--- a/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
+++ b/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
@@ -14,17 +14,16 @@
     <sheet name="Esquadrão de Combate" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Preços Atuais" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Radar ML" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Desempenho Próprio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Google Shopping" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Keywords &amp; Leilão" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Concorrentes Descobertos" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Histórico Preço x Ads" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="GA4 Funil" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="GA4 Canais" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="GA4 Landing Pages" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="GA4 Diagnóstico" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Catálogo" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Limitações" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Google Shopping" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Keywords &amp; Leilão" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Concorrentes Descobertos" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Histórico Preço x Ads" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="GA4 Funil" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="GA4 Canais" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="GA4 Landing Pages" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="GA4 Diagnóstico" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Catálogo" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Limitações" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,15 +58,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00B00020"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B00020"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,6 +85,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C0392B"/>
       </patternFill>
     </fill>
@@ -100,16 +106,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0027AE60"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF4E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,9 +121,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,24 +131,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -544,358 +537,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CAMPANHA</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>KEYWORD</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>IMPRESSIONS</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>CLICKS</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>CPC_MEDIO</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>QUALITY_SCORE</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>IMPRESSION_SHARE</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>RANK_LOST</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>DOMINIOS_NO_LEILAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Brand.</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>joie suplementos</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="n">
-        <v>5200</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>890</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>97</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Brand.</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>joie</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>540</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Search.</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>suplementos alimentares</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Search.</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>whey protein</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>1450</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Search - Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>whey protein isolado</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>1320</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>gsuplementos.com.br (1x), vitafor.com.br (1x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Search.</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>omega 3</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>980</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Search.</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>polivitamínico</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>860</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Search - Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>creatina monohidratada</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>640</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>gsuplementos.com.br (1x), vitafor.com.br (1x)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -940,516 +581,516 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>SKIN DOCTOR OFICIAL</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="5" t="n">
         <v>0.707</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>descoberta_ml</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Sérum Facial Skin Doctor Vitamina C</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>presenca_ads, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>BLACK SKULL</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="5" t="n">
         <v>0.695</v>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>descoberta_ml</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Sérum Facial Vitamina C Black Skull 30ml</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>VULT COSMETICOS</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="5" t="n">
         <v>0.605</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>descoberta_ml</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Sérum Vitamina C Vult 30ml</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>presenca_ads, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Max Titanium</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>maxtitanium.com.br</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>CENTRUM OFICIAL</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5" t="n">
         <v>0.696</v>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>descoberta_ml</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Multivitamínico Feminino Centrum</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>presenca_ads, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>GROWTH SUPPLEMENTS</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="5" t="n">
         <v>0.614</v>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>descoberta_ml</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Polivitamínico Feminino Growth 60 cápsulas</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Amaze</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Max Titanium</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>maxtitanium.com.br</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>BLACK SKULL</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="5" t="n">
         <v>0.8139999999999999</v>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>descoberta_ml</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Whey Protein Isolado Black Skull 900g</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Max Titanium</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="5" t="n">
         <v>0.658</v>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>manual, descoberta_ml</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Whey Protein Concentrado Max Titanium 900g</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>GROWTH SUPPLEMENTS</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="5" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>descoberta_ml</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Whey Protein Isolado Growth 900g</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Creatina Joie</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>BLACK SKULL</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="5" t="n">
         <v>0.759</v>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>descoberta_ml</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Creatina Black Skull Creatine 300g</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>preco, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Creatina Joie</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Max Titanium</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="5" t="n">
         <v>0.66</v>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>manual, descoberta_ml</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Creatina Monohidratada Max Titanium 300g</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>preco, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Creatina Joie</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>GROWTH SUPPLEMENTS</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="5" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>descoberta_ml</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Creatina Monohidratada Growth 300g</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>preco, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>(global — leilão)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Max Titanium</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>manual, auction_insight</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>maxtitanium.com.br</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>(global — leilão)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>mercadolivre.com.br</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>auction_insight</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>mercadolivre.com.br</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>(global — leilão)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>gsuplementos.com.br</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>auction_insight</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>gsuplementos.com.br</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>(global — leilão)</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>vitafor.com.br</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>auction_insight</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>vitafor.com.br</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
         </is>
@@ -1460,7 +1101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1668,142 +1309,142 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="6" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="12" t="n">
+      <c r="E6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="12" t="b">
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="6" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="12" t="n">
+      <c r="E7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="12" t="b">
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="6" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="12" t="n">
+      <c r="E8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="12" t="b">
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="6" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="E9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="12" t="n">
+      <c r="E9" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="12" t="b">
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1878,208 +1519,208 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="6" t="n">
         <v>119.9</v>
       </c>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n">
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" s="12" t="b">
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="6" t="n">
         <v>129.9</v>
       </c>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n">
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" s="12" t="b">
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="6" t="n">
         <v>129.9</v>
       </c>
-      <c r="E14" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="12" t="n">
+      <c r="E14" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" s="12" t="b">
+      <c r="G14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="6" t="n">
         <v>129.9</v>
       </c>
-      <c r="E15" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="12" t="n">
+      <c r="E15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" s="12" t="b">
+      <c r="G15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="6" t="n">
         <v>129.9</v>
       </c>
-      <c r="E16" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="12" t="n">
+      <c r="E16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="12" t="b">
+      <c r="G16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="6" t="n">
         <v>129.9</v>
       </c>
-      <c r="E17" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="12" t="n">
+      <c r="E17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" s="12" t="b">
+      <c r="G17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2088,7 +1729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2218,29 +1859,29 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="6" t="n">
         <v>528</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="6" t="n">
         <v>0.026</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="6" t="n">
         <v>0.1775</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="6" t="n">
         <v>2446</v>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>begin_checkout</t>
         </is>
@@ -2276,7 +1917,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2918,7 +2559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3160,33 +2801,33 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>/garrafa-copa-joie/p</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="7" t="n">
         <v>493</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="7" t="n">
         <v>0.6531</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="7" t="n">
         <v>0.3469</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="7" t="n">
         <v>1.44421906693712</v>
       </c>
-      <c r="F8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="F8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3280,99 +2921,99 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>/colageno-verisol-em-po---sabor-frutas-vermelhas-450g/p</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="7" t="n">
         <v>293</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="7" t="n">
         <v>0.2389</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="7" t="n">
         <v>0.7611</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="7" t="n">
         <v>0.07508532423208192</v>
       </c>
-      <c r="F12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="F12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>(sem página)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="7" t="n">
         <v>288</v>
       </c>
-      <c r="C13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="13" t="n">
+      <c r="C13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="n">
         <v>0.1388888888888889</v>
       </c>
-      <c r="F13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="F13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>(not set)</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="7" t="n">
         <v>274</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="7" t="n">
         <v>0.0292</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="7" t="n">
         <v>0.9708</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="7" t="n">
         <v>0.0145985401459854</v>
       </c>
-      <c r="F14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="F14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3408,165 +3049,165 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>/faciderm---colageno-hidrolisado-e-vitamina-c-120-capsulas---135g---vitamina-para-a-pele-do-rosto/p</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="7" t="n">
         <v>124</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="7" t="n">
         <v>0.2984</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="7" t="n">
         <v>0.7016</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="7" t="n">
         <v>0.06451612903225806</v>
       </c>
-      <c r="F16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="F16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>/kit-magnesio-quelato-mais-colageno-verisol---joie-suplementos/p</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="7" t="n">
         <v>115</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="7" t="n">
         <v>0.3304</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="7" t="n">
         <v>0.6696</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="7" t="n">
         <v>0.01739130434782609</v>
       </c>
-      <c r="F17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
+      <c r="F17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>/fale-conosco</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="7" t="n">
         <v>0.6339</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="7" t="n">
         <v>0.3661</v>
       </c>
-      <c r="E18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="E18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>/curcuma-e-vitamina-c-joie---60-capsulas-600mg---auxilia-a-aumentar-a-imunidade/p</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="7" t="n">
         <v>0.2883</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="7" t="n">
         <v>0.7117</v>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="E19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>/colageno-verisol-em-po---sabor-limao-450g/p</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="7" t="n">
         <v>104</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="7" t="n">
         <v>0.2308</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="7" t="n">
         <v>0.7692</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="7" t="n">
         <v>0.0576923076923077</v>
       </c>
-      <c r="F20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -3606,7 +3247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3638,102 +3279,102 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Maior vazamento do funil: Checkout</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Só 17.8% da etapa anterior chega em 'Checkout' (528 de 2,974). É onde a correção tem o maior efeito absoluto no número de compras.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Canal 'Paid Shopping' traz volume e não converte</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>943 sessões e 0 compra(s) no período, com 449 adições ao carrinho. Checar rastreamento de conversão desse canal antes de concluir que é audiência ruim — volume alto com zero compra costuma ser tag/atribuição.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Engajamento de 'Direct' muito abaixo da mediana</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>27.1% de sessões engajadas contra mediana de 46.6% entre os canais, sobre 2,891 sessões. Sinal clássico de descasamento entre criativo/segmentação e a página de destino.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Engajamento de 'Unassigned' muito abaixo da mediana</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>23.2% de sessões engajadas contra mediana de 46.6% entre os canais, sobre 676 sessões. Sinal clássico de descasamento entre criativo/segmentação e a página de destino.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Engajamento de 'Paid Social' muito abaixo da mediana</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>18.4% de sessões engajadas contra mediana de 46.6% entre os canais, sobre 2,683 sessões. Sinal clássico de descasamento entre criativo/segmentação e a página de destino.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>9 landing page(s) com tráfego e nenhuma compra</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Maiores: /garrafa-copa-joie/p (493 sessões, 712 no carrinho); /colageno-verisol-em-po---sabor-frutas-vermelhas-450g/p (293 sessões, 22 no carrinho); (sem página) (288 sessões, 40 no carrinho). Priorize por sessão perdida, não por número de páginas.</t>
         </is>
@@ -3745,12 +3386,12 @@
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Concentração por dispositivo</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>mobile concentra 74% da receita. Pior conversão entre devices com volume: mobile (0.87%).</t>
         </is>
@@ -3762,12 +3403,12 @@
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Dependência de cliente novo</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>82% dos compradores do período compraram pela primeira vez (155 de 188). Quanto mais alto, mais o faturamento depende de aquisição paga e menos de base.</t>
         </is>
@@ -3778,7 +3419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3974,7 +3615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3988,96 +3629,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>O que este relatório CAPTURA automaticamente</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr"/>
+      <c r="B1" s="5" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Mercado Livre</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Preço, preço original, desconto, posição na busca e reviews de cada concorrente cadastrado, comparados com a rodada anterior.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr"/>
-      <c r="B3" s="6" t="inlineStr"/>
+      <c r="A3" s="5" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>O que NÃO captura</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Investimento real (R$) em Google Ads ou Meta Ads</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Não existe fonte pública para o gasto de terceiros em nenhuma plataforma. Não é estimado, não é inventado.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Anúncios pagos do Google na SERP</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>O scraper de SERP usado não retorna paidResults/paidProducts — confirmado vazio mesmo em termos com anúncio comprovado.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Contagem de anúncios ativos (Meta Ad Library / Google Ads Transparency Center)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>É sinal de ATIVIDADE, não de valor gasto, e hoje é capturado manualmente via --ads-manual (o script não navega esses painéis sozinho).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Posição no Mercado Livre = patrocinado?</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>O scraper não confirma se um item específico é Mercado Ads ou orgânico — subida de posição é tratada como proxy, não prova.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="6" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Como cobrir melhor o pago</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Veja references/fontes-e-limitacoes.md e a skill brand-bidding-monitor para os métodos manuais completos (SERP, Ad Library, Ads Transparency Center, Auction Insights).</t>
         </is>
@@ -4111,7 +3752,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gerado em 2026-08-02 02:50 UTC | cadência sugerida: 6h</t>
+          <t>Gerado em 2026-08-02 10:11 UTC | cadência sugerida: 6h</t>
         </is>
       </c>
     </row>
@@ -4138,7 +3779,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4148,7 +3789,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4168,7 +3809,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4214,7 +3855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4287,348 +3928,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>queda_preco</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>agressiva</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull baixou o preço de 'Faciderm' de R$ 89.90 para R$ 71.90 (-20.0%).</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Sinal de liquidação de estoque, novo substituto ou guerra de preço deliberada. Risco alto de canibalização no curto prazo.</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>Estimativa por elasticidade deve ser tratada como piso — quedas agressivas convertem desproporcionalmente mais (efeito ancoragem). Estimativa: +30.0% de deslocamento de demanda (a seu favor), usando elasticidade configurada (-1.5) x variação de preço observada (-20.0%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 104.90, ROAS 5.00, CTR 6.47% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Price-match seletivo só nos SKUs mais expostos, não na linha toda; Reforçar prova social (reviews/garantia) para justificar não seguir a queda; Campanha de retenção/e-mail para base já convertida; Checar se é liquidação temporária antes de comprometer margem de forma permanente</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Margem de contribuição, ROAS, CAC, Share of search/Buy Box, Taxa de conversão, Ticket médio</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>novo_desconto</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull passou a oferecer 20% de desconto em 'Faciderm' (antes 0%).</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Desconto por tempo limitado costuma converter mais rápido que uma baixa de preço permanente (efeito urgência).</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Tratar como a queda de preço equivalente, com efeito concentrado na janela do cupom (não distribuído).</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Cupom-espelho de curta duração no produto equivalente; Destacar frete grátis/parcelamento se não puder cobrir o desconto; Se o cupom for sazonal (Black Friday etc.), sincronizar campanha própria à mesma data em vez de reagir isolado</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>CTR, Taxa de conversão, CAC no período do cupom, ROAS da campanha ativa</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>novo_entrante</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Growth Supplements apareceu pela 1a vez na busca de 'Faciderm' (posição 2).</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Aumento da concorrência direta no mesmo termo de busca; dilui share entre mais players.</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Risco difuso, maior quanto mais barato/melhor avaliado for o novo entrante.</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Cadastrar o novo concorrente no config.json para monitorar nas próximas rodadas; Avaliar se ele compete por preço, marca ou diferencial de produto para calibrar a resposta</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Share of search, Posição média, Taxa de conversão</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/growth-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>salto_visibilidade_ml</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull ganhou visibilidade em 'Amaze': subiu da posição 4 para 1 e reviews de 60 para 95.</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Mais impressões para o concorrente no mesmo termo; nas primeiras posições do ML o CTR cai muito rápido por posição perdida.</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Correlacionado com perda de share of search; não quantificável com precisão sem dados de leilão — tratar como alerta de atenção.</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Revisar ficha do produto próprio (título, imagens, reviews, perguntas respondidas); Considerar aumentar lance de Mercado Ads no termo, se já houver campanha ativa; Checar se o concorrente lançou promoção/frete que também ajuda o ranqueamento</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Posição média na busca, CTR, Taxa de conversão, Impression share (Mercado Ads)</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-amaze</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>concorrente_sumiu</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Growth Supplements sumiu da busca de 'Amaze' (estava na posição 1). Hipótese: ruptura de estoque ou pausa de campanha — não confirmado.</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Janela de oportunidade temporária — menos competição direta pelo termo/posição.</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Oportunidade de ganho de share enquanto durar; não é permanente até confirmar (pode ser reposição de estoque em dias).</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Aumentar temporariamente investimento em mídia no termo/SKU equivalente para capturar a demanda órfã; Não reduzir preço proativamente — a demanda já não tem para onde ir</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Share of search, Volume/conversão do SKU equivalente, ROAS</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/growth-amaze</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>aumento_preco_concorrente</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>moderada</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull subiu o preço de 'Linha Joie Fit' de R$ 119.90 para R$ 129.90 (+8.3%).</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Janela real de oportunidade para ganhar posição/Buy Box e volume sem sacrificar margem.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Ganho potencial relevante (ver estimativa por elasticidade, sentido positivo). Estimativa: -12.5% de deslocamento de demanda (a favor do concorrente), usando elasticidade configurada (-1.5) x variação de preço observada (+8.3%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 134.49, ROAS 3.55, CTR 2.29% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Reforçar investimento em mídia paga no SKU equivalente enquanto a vantagem dura; Atualizar comparativos de preço em conteúdo/anúncio</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Share of search/impressões, ROAS, CAC</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-whey</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4640,7 +3939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4719,378 +4018,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>alta</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-02 02:50 UTC</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>queda_preco</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>agressiva</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Black Skull baixou o preço de 'Faciderm' de R$ 89.90 para R$ 71.90 (-20.0%).</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Sinal de liquidação de estoque, novo substituto ou guerra de preço deliberada. Risco alto de canibalização no curto prazo.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Estimativa por elasticidade deve ser tratada como piso — quedas agressivas convertem desproporcionalmente mais (efeito ancoragem). Estimativa: +30.0% de deslocamento de demanda (a seu favor), usando elasticidade configurada (-1.5) x variação de preço observada (-20.0%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 104.90, ROAS 5.00, CTR 6.47% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Price-match seletivo só nos SKUs mais expostos, não na linha toda; Reforçar prova social (reviews/garantia) para justificar não seguir a queda; Campanha de retenção/e-mail para base já convertida; Checar se é liquidação temporária antes de comprometer margem de forma permanente</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Margem de contribuição, ROAS, CAC, Share of search/Buy Box, Taxa de conversão, Ticket médio</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-02 02:50 UTC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>novo_desconto</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Black Skull passou a oferecer 20% de desconto em 'Faciderm' (antes 0%).</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Desconto por tempo limitado costuma converter mais rápido que uma baixa de preço permanente (efeito urgência).</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Tratar como a queda de preço equivalente, com efeito concentrado na janela do cupom (não distribuído).</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Cupom-espelho de curta duração no produto equivalente; Destacar frete grátis/parcelamento se não puder cobrir o desconto; Se o cupom for sazonal (Black Friday etc.), sincronizar campanha própria à mesma data em vez de reagir isolado</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>CTR, Taxa de conversão, CAC no período do cupom, ROAS da campanha ativa</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-02 02:50 UTC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>novo_entrante</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Growth Supplements apareceu pela 1a vez na busca de 'Faciderm' (posição 2).</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Aumento da concorrência direta no mesmo termo de busca; dilui share entre mais players.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Risco difuso, maior quanto mais barato/melhor avaliado for o novo entrante.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Cadastrar o novo concorrente no config.json para monitorar nas próximas rodadas; Avaliar se ele compete por preço, marca ou diferencial de produto para calibrar a resposta</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Share of search, Posição média, Taxa de conversão</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/growth-faciderm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-02 02:50 UTC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>salto_visibilidade_ml</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Black Skull ganhou visibilidade em 'Amaze': subiu da posição 4 para 1 e reviews de 60 para 95.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Mais impressões para o concorrente no mesmo termo; nas primeiras posições do ML o CTR cai muito rápido por posição perdida.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Correlacionado com perda de share of search; não quantificável com precisão sem dados de leilão — tratar como alerta de atenção.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Revisar ficha do produto próprio (título, imagens, reviews, perguntas respondidas); Considerar aumentar lance de Mercado Ads no termo, se já houver campanha ativa; Checar se o concorrente lançou promoção/frete que também ajuda o ranqueamento</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Posição média na busca, CTR, Taxa de conversão, Impression share (Mercado Ads)</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-amaze</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-02 02:50 UTC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>concorrente_sumiu</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Growth Supplements sumiu da busca de 'Amaze' (estava na posição 1). Hipótese: ruptura de estoque ou pausa de campanha — não confirmado.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Janela de oportunidade temporária — menos competição direta pelo termo/posição.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Oportunidade de ganho de share enquanto durar; não é permanente até confirmar (pode ser reposição de estoque em dias).</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Aumentar temporariamente investimento em mídia no termo/SKU equivalente para capturar a demanda órfã; Não reduzir preço proativamente — a demanda já não tem para onde ir</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Share of search, Volume/conversão do SKU equivalente, ROAS</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/growth-amaze</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-08-02 02:50 UTC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>aumento_preco_concorrente</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>moderada</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Black Skull subiu o preço de 'Linha Joie Fit' de R$ 119.90 para R$ 129.90 (+8.3%).</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Janela real de oportunidade para ganhar posição/Buy Box e volume sem sacrificar margem.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Ganho potencial relevante (ver estimativa por elasticidade, sentido positivo). Estimativa: -12.5% de deslocamento de demanda (a favor do concorrente), usando elasticidade configurada (-1.5) x variação de preço observada (+8.3%). Premissa, não dado medido. Desempenho próprio atual no produto (Google/Meta Ads, últimos dados importados): CPA R$ 134.49, ROAS 3.55, CTR 2.29% — use como referência real para decidir quanto de margem cabe sacrificar num price-match.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Reforçar investimento em mídia paga no SKU equivalente enquanto a vantagem dura; Atualizar comparativos de preço em conteúdo/anúncio</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Share of search/impressões, ROAS, CAC</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://mercadolivre.com.br/simulado/black-skull-whey</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5102,7 +4029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5142,198 +4069,6 @@
       <c r="F1" s="4" t="inlineStr">
         <is>
           <t>RESUMO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Agente de Precificação e Margem</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>AGUARDANDO AUTORIZAÇÃO</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>queda_preco</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull baixou o preço de 'Faciderm' de R$ 89.90 para R$ 71.90 (-20.0%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Agente de Precificação e Margem</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>MONITORANDO</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>novo_desconto</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull passou a oferecer 20% de desconto em 'Faciderm' (antes 0%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Agente de Marketplace (Mercado Livre Ops)</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>MONITORANDO</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>novo_entrante</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Growth Supplements apareceu pela 1a vez na busca de 'Faciderm' (posição 2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Agente de Marketplace (Mercado Livre Ops)</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>MONITORANDO</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>salto_visibilidade_ml</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull ganhou visibilidade em 'Amaze': subiu da posição 4 para 1 e reviews de 60 para 95.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Agente de Marketplace (Mercado Livre Ops)</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>MONITORANDO</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>concorrente_sumiu</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Growth Supplements sumiu da busca de 'Amaze' (estava na posição 1). Hipótese: ruptura de estoque ou pausa de campanha — não confirmado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Agente de Precificação e Margem</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>MONITORANDO</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>aumento_preco_concorrente</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull subiu o preço de 'Linha Joie Fit' de R$ 119.90 para R$ 129.90 (+8.3%).</t>
         </is>
       </c>
     </row>
@@ -5604,7 +4339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5668,7 +4403,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amaze</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5680,202 +4415,97 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>84.90000000000001</v>
+        <v>129.9</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>910</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>340</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H3" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>desconhecido</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>365</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>910</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>480</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H5" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>desconhecido</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" t="n">
-        <v>365</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H8" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>desconhecido</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>95</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.3</v>
       </c>
     </row>
   </sheetData>
@@ -5889,253 +4519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>PRODUTO</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>SPEND</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>IMPRESSIONS</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>CLICKS</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>CTR_PCT</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>CPC</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>CONVERSIONS</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>CONVERSIONS_VALUE</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>CPA</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>ROAS</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>GA4_SESSIONS</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>GA4_ENGAJAMENTO_PCT</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>GA4_CONVERSAO_PCT</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>CAMPANHAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2596.9507</v>
-      </c>
-      <c r="C2" t="n">
-        <v>34496</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2231</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6.467416512059369</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.164029896907216</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.757</v>
-      </c>
-      <c r="H2" t="n">
-        <v>12992.9542</v>
-      </c>
-      <c r="I2" t="n">
-        <v>104.8976329926889</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5.003157818898911</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1912</v>
-      </c>
-      <c r="L2" t="n">
-        <v>47.90794979079498</v>
-      </c>
-      <c r="M2" t="n">
-        <v>19.08995815899582</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>google_ads:Pmax - Faciderm.; googleanalytics4:Pmax - Faciderm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2015.590999999999</v>
-      </c>
-      <c r="C3" t="n">
-        <v>49644</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1303</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.624687776972041</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.546884881043745</v>
-      </c>
-      <c r="G3" t="n">
-        <v>15.6831</v>
-      </c>
-      <c r="H3" t="n">
-        <v>8535.625499999998</v>
-      </c>
-      <c r="I3" t="n">
-        <v>128.5199354719411</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.234800363764275</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1011</v>
-      </c>
-      <c r="L3" t="n">
-        <v>53.41246290801187</v>
-      </c>
-      <c r="M3" t="n">
-        <v>23.63996043521266</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>google_ads:Pmax - Amaze.; googleanalytics4:Pmax - Amaze.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2312.5504</v>
-      </c>
-      <c r="C4" t="n">
-        <v>62051</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1421</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.290051731640102</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.627410555946516</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17.1951</v>
-      </c>
-      <c r="H4" t="n">
-        <v>8213.5782</v>
-      </c>
-      <c r="I4" t="n">
-        <v>134.4889183546475</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.551740191262426</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1543</v>
-      </c>
-      <c r="L4" t="n">
-        <v>44.19961114711601</v>
-      </c>
-      <c r="M4" t="n">
-        <v>7.906675307841867</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>google_ads:Pmax - Linha Joie Fit; google_ads:Search - Linha Joie Fit; googleanalytics4:Search - Linha Joie Fit; googleanalytics4:Pmax - Linha Joie Fit; googleanalytics4:🟩 - [[Tráfego]] - [Linha Joie Fit] - [Carrossel] - Whey Silk Protein; googleanalytics4:🟩 - [[Tráfego]] - [Linha Joie Fit] - [Carrossel] - Colágeno</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6197,35 +4581,35 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="11" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H2" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>640</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
@@ -6234,42 +4618,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amaze</t>
+          <t>Linha Joie Fit</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Growth Supplements</t>
+          <t>Max Titanium</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>76.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6281,16 +4665,16 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>124.9</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>640</v>
+        <v>210</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -6304,140 +4688,387 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Amaze</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Max Titanium</t>
+          <t>Growth Supplements</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>89.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>310</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>CAMPANHA</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>KEYWORD</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>CLICKS</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>CPC_MEDIO</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>QUALITY_SCORE</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>IMPRESSION_SHARE</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>RANK_LOST</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>DOMINIOS_NO_LEILAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>joie suplementos</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>890</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>joie</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>3100</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>540</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>suplementos alimentares</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>whey protein</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>whey protein isolado</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1320</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (1x), vitafor.com.br (1x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>omega 3</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>980</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="11" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H6" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>nao</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="E7" t="n">
-        <v>17</v>
-      </c>
-      <c r="F7" t="n">
-        <v>210</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>sim</t>
+      <c r="G7" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>NÓS</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>95</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H8" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>sim</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>polivitamínico</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>860</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>creatina monohidratada</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (1x), vitafor.com.br (1x)</t>
         </is>
       </c>
     </row>

--- a/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
+++ b/war-room-concorrencia/contexto-e-apoio/arquivos-finais/war-room.xlsx
@@ -7,23 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="⚠ Keywords é simulado" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Battlecards" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Alertas (histórico)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Esquadrão de Combate" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Preços Atuais" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Radar ML" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Google Shopping" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Keywords &amp; Leilão" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Concorrentes Descobertos" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Histórico Preço x Ads" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="GA4 Funil" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="GA4 Canais" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="GA4 Landing Pages" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="GA4 Diagnóstico" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Catálogo" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Limitações" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Battlecards" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Alertas (histórico)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Esquadrão de Combate" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Preços Atuais" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Radar ML" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Desempenho Próprio" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Keywords &amp; Leilão" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Concorrentes Descobertos" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Histórico Preço x Ads" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="GA4 Funil" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="GA4 Canais" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="GA4 Landing Pages" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="GA4 Diagnóstico" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Catálogo" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Limitações" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,8 +57,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00B00020"/>
-      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -123,14 +120,12 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -513,16 +508,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Este relatório de keywords usa DADO SIMULADO — o Google Ads ainda não está conectado no Windsor.ai desta integração. Ver references/fontes-e-limitacoes.md.</t>
+          <t>War Room — Joie</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Gerado em 2026-08-02 17:24 UTC | cadência sugerida: 6h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>VALOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alertas nesta rodada — severidade ALTA</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Alertas nesta rodada — severidade MÉDIA</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alertas nesta rodada — severidade BAIXA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total de alertas acumulados no histórico</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Produtos monitorados</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Concorrentes monitorados</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Investimento real em ads capturado</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0 — não é dado público (ver aba Limitações)</t>
         </is>
       </c>
     </row>
@@ -537,577 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>PRODUTO</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>CANDIDATO</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>SCORE</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>ORIGEM</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>TITULO_VARIANTE</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>COMPONENTES_SEM_DADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>SKIN DOCTOR OFICIAL</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Sérum Facial Skin Doctor Vitamina C</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>presenca_ads, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>BLACK SKULL</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Sérum Facial Vitamina C Black Skull 30ml</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>VULT COSMETICOS</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Sérum Vitamina C Vult 30ml</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>presenca_ads, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Max Titanium</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>maxtitanium.com.br</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>CENTRUM OFICIAL</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Multivitamínico Feminino Centrum</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>presenca_ads, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>GROWTH SUPPLEMENTS</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Polivitamínico Feminino Growth 60 cápsulas</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Max Titanium</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>maxtitanium.com.br</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>BLACK SKULL</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Whey Protein Isolado Black Skull 900g</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Max Titanium</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>manual, descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Whey Protein Concentrado Max Titanium 900g</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>GROWTH SUPPLEMENTS</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Whey Protein Isolado Growth 900g</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Creatina Joie</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>BLACK SKULL</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Creatina Black Skull Creatine 300g</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>preco, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Creatina Joie</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Max Titanium</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>manual, descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Creatina Monohidratada Max Titanium 300g</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>preco, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Creatina Joie</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>GROWTH SUPPLEMENTS</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>descoberta_ml</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Creatina Monohidratada Growth 300g</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>preco, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>(global — leilão)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Max Titanium</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>manual, auction_insight</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>maxtitanium.com.br</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>(global — leilão)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>mercadolivre.com.br</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>auction_insight</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>mercadolivre.com.br</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>(global — leilão)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>gsuplementos.com.br</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>auction_insight</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>gsuplementos.com.br</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>(global — leilão)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>vitafor.com.br</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>auction_insight</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>vitafor.com.br</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1122,47 +643,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>CONCORRENTE</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>PRECO</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>TEM_ADS</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>NOSSA_POSICAO</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>CONCORRENTE_POSICAO</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>DISPUTANDO_DIRETO</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>KPI_QUEDA</t>
         </is>
@@ -1181,20 +702,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-02 10:02 UTC</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -1216,20 +731,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-02 10:03 UTC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -1251,20 +760,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02 10:05 UTC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="E4" t="b">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -1286,21 +789,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-02 10:06 UTC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="E5" t="b">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
@@ -1309,37 +806,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:10 UTC</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E6" s="6" t="b">
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="6" t="b">
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1356,15 +847,13 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-02 17:24 UTC</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E7" s="6" t="b">
-        <v>1</v>
-      </c>
+      <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n">
         <v>3</v>
       </c>
@@ -1375,103 +864,85 @@
         <v>1</v>
       </c>
       <c r="I7" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="E8" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="b">
-        <v>1</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:02 UTC</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Faciderm</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="E9" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6" t="b">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:03 UTC</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Black Skull</t>
+          <t>Growth Supplements</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-02 10:05 UTC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>119.9</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -1486,27 +957,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Black Skull</t>
+          <t>Growth Supplements</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-02 10:06 UTC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>119.9</v>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -1519,63 +984,59 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>119.9</v>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="b">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:10 UTC</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Faciderm</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Black Skull</t>
+          <t>Growth Supplements</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-02 17:24 UTC</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>129.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="6" t="b">
         <v>1</v>
@@ -1585,142 +1046,358 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Linha Joie Fit</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:02 UTC</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>129.9</v>
       </c>
-      <c r="E14" s="6" t="b">
+      <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:03 UTC</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:05 UTC</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:06 UTC</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:10 UTC</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02 17:24 UTC</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="6" t="b">
+      <c r="H19" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="I14" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="I19" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E15" s="6" t="b">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:02 UTC</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" s="6" t="n">
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:03 UTC</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="6" t="b">
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:05 UTC</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="G22" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Black Skull</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E16" s="6" t="b">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:06 UTC</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="G23" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="6" t="n">
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:10 UTC</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="G24" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="6" t="b">
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-02 17:24 UTC</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="E17" s="6" t="b">
+      <c r="H25" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="F17" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" s="6" t="b">
+      <c r="I25" s="6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1729,7 +1406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1748,37 +1425,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ETAPA</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>% DO TOPO</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>% DA ANTERIOR</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>PERDIDOS</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>MAIOR VAZAMENTO</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>EVENTO</t>
         </is>
@@ -1917,7 +1594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1941,62 +1618,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>CANAL</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DECISAO</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>SESSIONS</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ENGAGEMENT_RATE</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>TX_CARRINHO</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>TX_CHECKOUT_P_CARRINHO</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>TX_COMPRA_P_CHECKOUT</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>TX_CONVERSAO</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>COMPRAS</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>RECEITA</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>RECEITA_POR_SESSAO</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>TICKET_MEDIO</t>
         </is>
@@ -2559,7 +2236,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2580,47 +2257,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>PAGINA</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>SESSIONS</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ENGAGEMENT_RATE</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>BOUNCE_RATE</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>TX_CARRINHO</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>COMPRAS</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>TX_CONVERSAO</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>RECEITA</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>SEM_COMPRA</t>
         </is>
@@ -3247,7 +2924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3262,17 +2939,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>NÍVEL</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ACHADO</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>DETALHE</t>
         </is>
@@ -3419,13 +3096,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3435,22 +3112,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>NOME</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>MONITORANDO?</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>DETALHE</t>
         </is>
@@ -3607,6 +3284,116 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>maxtitanium.com.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Concorrente</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Renovabe</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>candidato</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>renovabe.com.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Concorrente</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Soldiers Nutrition</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>candidato</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>soldiersnutrition.com.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Concorrente</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dark Lab Suplementos</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>candidato</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>darklabsuplementos.com.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Concorrente</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Coompare</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>candidato</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>coompare.com.br</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Concorrente</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vivatrue</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>candidato</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>vivatrue.com.br</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3730,126 +3517,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>War Room — Joie</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Gerado em 2026-08-02 10:11 UTC | cadência sugerida: 6h</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>INDICADOR</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>VALOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Alertas nesta rodada — severidade ALTA</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Alertas nesta rodada — severidade MÉDIA</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Alertas nesta rodada — severidade BAIXA</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Total de alertas acumulados no histórico</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Produtos monitorados</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Concorrentes monitorados</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Investimento real em ads capturado</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0 — não é dado público (ver aba Limitações)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3872,57 +3539,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>SEVERIDADE</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>NIVEL</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>CONCORRENTE</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>RESUMO</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>IMPACTO_CONCORRENCIA</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>IMPACTO_VOLUME</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>ESTRATEGIA_IMEDIATA</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>KPIS_IMPACTADOS</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>EVIDENCIA_URL</t>
         </is>
@@ -3933,7 +3600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3957,62 +3624,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>SEVERIDADE</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>NIVEL</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>CONCORRENTE</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>RESUMO</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>IMPACTO_CONCORRENCIA</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>IMPACTO_VOLUME</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>ESTRATEGIA_IMEDIATA</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>KPIS_IMPACTADOS</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>EVIDENCIA_URL</t>
         </is>
@@ -4023,7 +3690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4041,32 +3708,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>AGENTE</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>TIPO_ALERTA</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>CONCORRENTE</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>RESUMO</t>
         </is>
@@ -4077,7 +3744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4100,57 +3767,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>CONCORRENTE</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>SELLER</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>ORIGINAL_PRICE</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>DISCOUNT_PCT</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>POSITION</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>TOTAL_LISTAGENS</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>REVIEWS</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -4333,13 +4000,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4354,47 +4021,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>PRODUTO</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>QUEM</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>POSITION</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>DISCOUNT_PCT</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>REVIEWS</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>RATING</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>FRETE_GRATIS</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>PATROCINADO</t>
         </is>
@@ -4403,7 +4070,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Linha Joie Fit</t>
+          <t>Amaze</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4415,97 +4082,448 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>95</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>340</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>desconhecido</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>129.9</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>910</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>desconhecido</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Black Skull</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="n">
+        <v>365</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Growth Supplements</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>NÓS</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>desconhecido</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>PRODUTO</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>SPEND</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>CLICKS</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>CTR_PCT</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>CPC</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>CONVERSIONS</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>CONVERSIONS_VALUE</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>GA4_SESSIONS</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>GA4_ENGAJAMENTO_PCT</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>GA4_CONVERSAO_PCT</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>CAMPANHAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2596.9507</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34496</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2231</v>
+      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6.467416512059369</v>
       </c>
       <c r="F2" t="n">
-        <v>910</v>
+        <v>1.164029896907216</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8</v>
+        <v>24.757</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12992.9542</v>
+      </c>
+      <c r="I2" t="n">
+        <v>104.8976329926889</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5.003157818898911</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1912</v>
+      </c>
+      <c r="L2" t="n">
+        <v>47.90794979079498</v>
+      </c>
+      <c r="M2" t="n">
+        <v>19.08995815899582</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>google_ads:Pmax - Faciderm.; googleanalytics4:Pmax - Faciderm.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2015.590999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>49644</v>
       </c>
       <c r="D3" t="n">
-        <v>71.90000000000001</v>
+        <v>1303</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>2.624687776972041</v>
       </c>
       <c r="F3" t="n">
-        <v>365</v>
+        <v>1.546884881043745</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>15.6831</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8535.625499999998</v>
+      </c>
+      <c r="I3" t="n">
+        <v>128.5199354719411</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.234800363764275</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1011</v>
+      </c>
+      <c r="L3" t="n">
+        <v>53.41246290801187</v>
+      </c>
+      <c r="M3" t="n">
+        <v>23.63996043521266</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>google_ads:Pmax - Amaze.; googleanalytics4:Pmax - Amaze.</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2312.5504</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>62051</v>
       </c>
       <c r="D4" t="n">
-        <v>68.90000000000001</v>
+        <v>1421</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2.290051731640102</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>1.627410555946516</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>95</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.3</v>
+        <v>17.1951</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8213.5782</v>
+      </c>
+      <c r="I4" t="n">
+        <v>134.4889183546475</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.551740191262426</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1543</v>
+      </c>
+      <c r="L4" t="n">
+        <v>44.19961114711601</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7.906675307841867</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>google_ads:Pmax - Linha Joie Fit; google_ads:Search - Linha Joie Fit; googleanalytics4:Search - Linha Joie Fit; googleanalytics4:Pmax - Linha Joie Fit; googleanalytics4:🟩 - [[Tráfego]] - [Linha Joie Fit] - [Carrossel] - Whey Silk Protein; googleanalytics4:🟩 - [[Tráfego]] - [Linha Joie Fit] - [Carrossel] - Colágeno</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4519,219 +4537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>PRODUTO</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>QUEM</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>POSITION</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>PRICE</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>DISCOUNT_PCT</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>REVIEWS</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>RATING</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>FRETE_GRATIS</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>PATROCINADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>124.9</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>640</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Linha Joie Fit</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Max Titanium</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>310</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>nao</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Faciderm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Black Skull</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="E4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F4" t="n">
-        <v>210</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Amaze</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Growth Supplements</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>88</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4746,47 +4552,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>CAMPANHA</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>KEYWORD</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>IMPRESSIONS</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>CLICKS</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>CPC_MEDIO</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>QUALITY_SCORE</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>IMPRESSION_SHARE</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>RANK_LOST</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>DOMINIOS_NO_LEILAO</t>
         </is>
@@ -4795,31 +4601,31 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Brand.</t>
+          <t>Pmax - Todos os Produtos.</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>joie suplementos</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>5200</v>
+        <v>143291</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>890</v>
+        <v>3309</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.35</v>
+        <v>1.15</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>97</v>
+        <v>12.2</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
@@ -4830,31 +4636,33 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Brand.</t>
+          <t>Geração de demanda - Capitais</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>joie</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>3100</v>
+        <v>112698</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>540</v>
+        <v>3932</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>94.5</v>
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
@@ -4865,210 +4673,2034 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Search.</t>
+          <t>Shopping - Colageno</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>suplementos alimentares</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>2100</v>
+        <v>74061</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>75</v>
+        <v>1292</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1.05</v>
+        <v>0.34</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>50</v>
+        <v>32.7</v>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Search.</t>
+          <t>Pmax - Amaze.</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>whey protein</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1450</v>
+        <v>46920</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>62</v>
+        <v>1251</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>46</v>
+        <v>74.7</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Search - Linha Joie Fit</t>
+          <t>Pmax - Linha Joie Fit</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>whey protein isolado</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1320</v>
+        <v>43658</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>58</v>
+        <v>965</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>22</v>
+        <v>13.9</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>gsuplementos.com.br (1x), vitafor.com.br (1x)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Search.</t>
+          <t>Pmax - Faciderm.</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>omega 3</t>
+          <t>(sem termo)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>980</v>
+        <v>34358</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>40</v>
+        <v>2219</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>40</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Search.</t>
+          <t>Search - Linha Joie Fit</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>polivitamínico</t>
+          <t>whey protein</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>860</v>
+        <v>4436</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.89</v>
+        <v>2.43</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>42</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>maxtitanium.com.br (3x), mercadolivre.com.br (1x)</t>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>omega 3</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2355</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Joie</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2291</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>532</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), shopee.com.br (29x), vhita.com.br (27x), magazineluiza.com.br (17x), puravida.com.br (14x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>magnésio</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1347</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>suplementos alimentares</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1173</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Brand.</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Joie suplementos</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>424</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), shopee.com.br (29x), vhita.com.br (27x), magazineluiza.com.br (17x), puravida.com.br (14x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>Search - Linha Joie Fit</t>
         </is>
       </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Colageno</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>823</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>polivitaminico</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>461</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>magnésio quelato</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>456</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>vitamina D</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>309</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>whey protein sabor chocolate</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>magnésio quelato para que serve</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>colageno verisol</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>suplementos vitamínicos</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>colageno</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>suplemento de proteina e colageno verisol</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>whey protein</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>whey com colageno</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Ômega 3</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>suplemento para memoria</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>whey</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Colageno verisol</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>vitamina d3</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>colágeno verisol</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>suplemento para menopausa</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>suplemento para emagrecimento</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>vitamina d3 para que serve</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>cálcio</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>vitamina para os ossos</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>multivitamínico</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>suplementos para memoria</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>cartamo</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>polivitamínico</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>coezima q10</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Search.</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>testofen</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br (29x), puravida.com.br (29x), shopee.com.br (29x), vhita.com.br (29x), vitafor.com.br (27x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Search - Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>colageno hidrolisado verisol em po</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br (25x), mercadolivre.com.br (24x), puravida.com.br (24x), shopee.com.br (24x), maxtitanium.com.br (19x)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>PRODUTO</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>CANDIDATO</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>ORIGEM</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TITULO_VARIANTE</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>COMPONENTES_SEM_DADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>SKIN DOCTOR OFICIAL</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Sérum Facial Skin Doctor Vitamina C</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>presenca_ads, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>BLACK SKULL</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Sérum Facial Vitamina C Black Skull 30ml</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>VULT COSMETICOS</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Sérum Vitamina C Vult 30ml</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>presenca_ads, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Faciderm</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>CENTRUM OFICIAL</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Multivitamínico Feminino Centrum</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>presenca_ads, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>GROWTH SUPPLEMENTS</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Polivitamínico Feminino Growth 60 cápsulas</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Amaze</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>creatina monohidratada</t>
+          <t>BLACK SKULL</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>640</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>gsuplementos.com.br (1x), vitafor.com.br (1x)</t>
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Whey Protein Isolado Black Skull 900g</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>manual, descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Whey Protein Concentrado Max Titanium 900g</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Linha Joie Fit</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>GROWTH SUPPLEMENTS</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Whey Protein Isolado Growth 900g</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Creatina Joie</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>BLACK SKULL</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Creatina Black Skull Creatine 300g</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>preco, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Creatina Joie</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>manual, descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Creatina Monohidratada Max Titanium 300g</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>preco, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Creatina Joie</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>GROWTH SUPPLEMENTS</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>descoberta_ml</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Creatina Monohidratada Growth 300g</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>preco, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>(global — leilão)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Max Titanium</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>manual, auction_insight</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>maxtitanium.com.br</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>(global — leilão)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>auction_insight</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>mercadolivre.com.br</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>(global — leilão)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>auction_insight</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>gsuplementos.com.br</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>(global — leilão)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>vitafor.com.br</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>auction_insight</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>vitafor.com.br</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>preco, autoridade_marca, presenca_ads, vendas_marketplace, kpis_redes_sociais</t>
         </is>
       </c>
     </row>
